--- a/Result/profitability/8201.xlsx
+++ b/Result/profitability/8201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.91</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01250000000000004</v>
+        <v>0.03625000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>24.7275</v>
+        <v>26.44625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08500000000000003</v>
+        <v>0.10625</v>
       </c>
       <c r="N3" t="n">
-        <v>26.9475</v>
+        <v>28.00125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.88</v>
       </c>
       <c r="M4" t="n">
-        <v>0.215</v>
+        <v>0.22875</v>
       </c>
       <c r="N4" t="n">
-        <v>28.87625</v>
+        <v>29.9375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09750000000000003</v>
+        <v>0.12875</v>
       </c>
       <c r="N5" t="n">
-        <v>29.88875</v>
+        <v>30.39375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0.17125</v>
       </c>
       <c r="N6" t="n">
-        <v>30.65625</v>
+        <v>31.755</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.13625</v>
+        <v>0.14125</v>
       </c>
       <c r="N7" t="n">
-        <v>31.9525</v>
+        <v>33.2125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24</v>
+        <v>0.2550000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>34.01375</v>
+        <v>35.1075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>-0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03125000000000001</v>
+        <v>0.03125000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>34.34375</v>
@@ -1902,7 +1902,7 @@
         <v>-0.03374999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>34.63500000000001</v>
+        <v>34.635</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>115</v>
+      </c>
+      <c r="D75" t="n">
+        <v>78</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.09999999999999996</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.63875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.090909090909091</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3695101351351351</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.041666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.039999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1423036280380416</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
